--- a/public/TEMPLATE MENU UPLOAD DATA SISWA.xlsx
+++ b/public/TEMPLATE MENU UPLOAD DATA SISWA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ICT WORKS\4. ICT 2023-Sekarang ALL GO ON\Jogja Muallimat [2 VA BMI - DB 36 MYSQL]\22. (Jumat22mei26) penyiapan request sekolah muallimaat\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\yogyakarta_mualimat_penerimaan\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A9F127-8B62-435F-97AA-1C67C4E65A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA084614-A893-4D6F-8F9D-2159D5520D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11280" tabRatio="760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UPLOAD DATA SISWA (NIS saja)" sheetId="3" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="53">
   <si>
     <t>NIS</t>
   </si>
@@ -176,6 +176,12 @@
   </si>
   <si>
     <t>sedangkan kolom Alamat dan Ortu (nama perwakilan wali santri) bersifat opsional boleh di isi boleh tidak</t>
+  </si>
+  <si>
+    <t>ICT</t>
+  </si>
+  <si>
+    <t>TESTING</t>
   </si>
 </sst>
 </file>
@@ -582,20 +588,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C07DFD7-A58D-4253-97E0-76E101863EAE}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -624,7 +630,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1234567801</v>
       </c>
@@ -653,7 +659,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1234567802</v>
       </c>
@@ -682,7 +688,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1234567803</v>
       </c>
@@ -711,7 +717,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>1234567804</v>
       </c>
@@ -740,7 +746,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1234567805</v>
       </c>
@@ -751,10 +757,10 @@
         <v>42</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>21</v>
@@ -769,7 +775,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>1234567806</v>
       </c>
@@ -807,21 +813,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -853,7 +859,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1234567801</v>
       </c>
@@ -885,7 +891,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1234567802</v>
       </c>
@@ -917,7 +923,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1234567803</v>
       </c>
@@ -949,7 +955,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>1234567804</v>
       </c>
@@ -981,7 +987,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1234567805</v>
       </c>
@@ -1013,7 +1019,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>1234567806</v>
       </c>
@@ -1054,20 +1060,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59F0334D-BFBC-4261-A2C8-DF7F09422AEE}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -1096,7 +1102,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1234567801</v>
       </c>
@@ -1125,7 +1131,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1234567802</v>
       </c>
@@ -1154,7 +1160,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1234567803</v>
       </c>
@@ -1183,7 +1189,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>1234567804</v>
       </c>
@@ -1212,7 +1218,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1234567805</v>
       </c>
@@ -1241,7 +1247,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>1234567806</v>
       </c>
@@ -1279,59 +1285,59 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ACD2702-5769-414D-8DDB-A0ADB41CA288}">
   <dimension ref="A1:A13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>35</v>
       </c>
